--- a/diseases/d085/2015-2019.xlsx
+++ b/diseases/d085/2015-2019.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -2345,9 +2342,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3925,9 +3919,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5801,9 +5792,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -7971,9 +7959,6 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">

--- a/diseases/d085/2015-2019.xlsx
+++ b/diseases/d085/2015-2019.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>0.378949298678841</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -800,11 +800,11 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -813,42 +813,42 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -919,29 +919,29 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_HISTORY</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Toxóplasmasýking</t>
+          <t>Toxoplasmosis, congenital</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>national_registry_notifications</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1034,11 +1034,11 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -1047,42 +1047,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1144,93 +1144,104 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2015-02-01</t>
+          <t>2015-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2015-02</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
         <v>2</v>
       </c>
-      <c r="O4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.008500056992882137</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1268,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1292,93 +1303,179 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
+          <t>2015-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2015-04</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Toxóplasmasýking</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
         <v>1</v>
       </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.004250028496441068</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1440,25 +1537,25 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2015-05-01</t>
+          <t>2015-02-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2015-05</t>
+          <t>2015-02</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.004250028496441068</v>
+        <v>0.008500056992882137</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1588,25 +1685,25 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2015-06-01</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2015-06</t>
+          <t>2015-04</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008500056992882137</v>
+        <v>0.004250028496441068</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1736,25 +1833,25 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2015-08-01</t>
+          <t>2015-05-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2015-08</t>
+          <t>2015-05</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.008500056992882137</v>
+        <v>0.004250028496441068</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1884,12 +1981,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2015-09-01</t>
+          <t>2015-06-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2015-09</t>
+          <t>2015-06</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -2032,12 +2129,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2015-11-01</t>
+          <t>2015-08-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2015-11</t>
+          <t>2015-08</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2180,25 +2277,25 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2015-09-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2015-12</t>
+          <t>2015-09</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.004250028496441068</v>
+        <v>0.008500056992882137</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -2298,12 +2395,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2328,104 +2425,93 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2016-01-01</t>
+          <t>2015-11-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2016-01</t>
+          <t>2015-11</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.008500056992882137</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -2452,17 +2538,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2487,179 +2573,93 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2016-01-01</t>
+          <t>2015-12-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2016-01</t>
+          <t>2015-12</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Toxóplasmasýking</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN13" t="b">
         <v>1</v>
       </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.004250028496441068</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -2691,12 +2691,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2721,93 +2721,104 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2016-02-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2016-02</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>195</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="R14" t="n">
-        <v>0.008479555315160162</v>
+        <v>0.299599663406692</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -2834,17 +2845,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2869,93 +2880,179 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2016-03</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N15" t="n">
+        <v>195</v>
+      </c>
+      <c r="O15" t="n">
+        <v>195</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN15" t="b">
         <v>1</v>
       </c>
-      <c r="O15" t="n">
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.004239777657580081</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -2987,12 +3084,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3017,93 +3114,104 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2016-04-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2016-04</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.004239777657580081</v>
+        <v>0</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -3130,17 +3238,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3165,93 +3273,179 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2016-06-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2016-06</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Toxóplasmasýking</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN17" t="b">
         <v>1</v>
       </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.004239777657580081</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -3313,25 +3507,25 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2016-07-01</t>
+          <t>2016-02-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2016-07</t>
+          <t>2016-02</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.004239777657580081</v>
+        <v>0.008479555315160162</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -3461,12 +3655,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2016-08-01</t>
+          <t>2016-03-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2016-08</t>
+          <t>2016-03</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3609,25 +3803,25 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2016-10-01</t>
+          <t>2016-04-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2016-10</t>
+          <t>2016-04</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.008479555315160162</v>
+        <v>0.004239777657580081</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -3757,25 +3951,25 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
+          <t>2016-06-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2016-12</t>
+          <t>2016-06</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.01271933297274024</v>
+        <v>0.004239777657580081</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -3875,12 +4069,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3905,104 +4099,93 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2016-07-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2016-07</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.004239777657580081</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -4029,17 +4212,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4064,179 +4247,93 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2016-08-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2016-08</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Toxóplasmasýking</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN23" t="b">
         <v>1</v>
       </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.004239777657580081</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -4298,25 +4395,25 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2016-10-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2017-01</t>
+          <t>2016-10</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.004231380697829149</v>
+        <v>0.008479555315160162</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -4446,12 +4543,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2017-02-01</t>
+          <t>2016-12-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2017-02</t>
+          <t>2016-12</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4464,7 +4561,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.01269414209348745</v>
+        <v>0.01271933297274024</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -4564,12 +4661,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4594,93 +4691,104 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2017-03</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>153</v>
       </c>
       <c r="O26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="R26" t="n">
-        <v>0.008462761395658299</v>
+        <v>0.2343578539658312</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -4707,17 +4815,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4742,93 +4850,179 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2017-05-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2017-05</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N27" t="n">
+        <v>153</v>
+      </c>
+      <c r="O27" t="n">
+        <v>153</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN27" t="b">
         <v>1</v>
       </c>
-      <c r="O27" t="n">
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.004231380697829149</v>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP27" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr"/>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -4860,12 +5054,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4890,93 +5084,104 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2017-06-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2017-06</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.01269414209348745</v>
+        <v>0</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -5003,17 +5208,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5038,93 +5243,179 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2017-07-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2017-07</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Toxóplasmasýking</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
         <v>2</v>
       </c>
-      <c r="O29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.008462761395658299</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP29" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr"/>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -5186,25 +5477,25 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2017-08-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2017-08</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0.0169255227913166</v>
+        <v>0.004231380697829149</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -5334,25 +5625,25 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2017-10-01</t>
+          <t>2017-02-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2017-10</t>
+          <t>2017-02</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0.004231380697829149</v>
+        <v>0.01269414209348745</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -5482,25 +5773,25 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2017-11-01</t>
+          <t>2017-03-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2017-11</t>
+          <t>2017-03</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0.0169255227913166</v>
+        <v>0.008462761395658299</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -5630,25 +5921,25 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2017-12-01</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2017-12</t>
+          <t>2017-05</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0.008462761395658299</v>
+        <v>0.004231380697829149</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -5748,12 +6039,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5778,104 +6069,93 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2017-06-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2017-06</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>0.01269414209348745</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -5902,17 +6182,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5937,179 +6217,93 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2017-07-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2017-07</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Toxóplasmasýking</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN35" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.008462761395658299</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6171,25 +6365,25 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2017-08-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2018-01</t>
+          <t>2017-08</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0.004226666844186674</v>
+        <v>0.0169255227913166</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -6319,25 +6513,25 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2018-02-01</t>
+          <t>2017-10-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2018-02</t>
+          <t>2017-10</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0.008453333688373348</v>
+        <v>0.004231380697829149</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -6467,25 +6661,25 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2018-03-01</t>
+          <t>2017-11-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2018-03</t>
+          <t>2017-11</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.004226666844186674</v>
+        <v>0.0169255227913166</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -6615,12 +6809,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2018-04-01</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2018-04</t>
+          <t>2017-12</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6633,7 +6827,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0.008453333688373348</v>
+        <v>0.008462761395658299</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -6733,12 +6927,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6763,93 +6957,104 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2018-05-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2018-05</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>151</v>
       </c>
       <c r="O40" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="R40" t="n">
-        <v>0.008453333688373348</v>
+        <v>0.230465589713176</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6876,17 +7081,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6911,93 +7116,179 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2018-06</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N41" t="n">
+        <v>151</v>
+      </c>
+      <c r="O41" t="n">
+        <v>151</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN41" t="b">
         <v>1</v>
       </c>
-      <c r="O41" t="n">
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT41" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0.004226666844186674</v>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP41" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
-      <c r="AT41" t="n">
-        <v>0</v>
-      </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -7029,12 +7320,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -7059,93 +7350,104 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2018-07</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0.004226666844186674</v>
+        <v>0</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -7172,17 +7474,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -7207,93 +7509,179 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2018-08-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2018-08</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Toxóplasmasýking</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT43" t="n">
         <v>2</v>
       </c>
-      <c r="O43" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0.008453333688373348</v>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP43" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr"/>
-      <c r="AT43" t="n">
-        <v>0</v>
-      </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -7355,25 +7743,25 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2018-09</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.008453333688373348</v>
+        <v>0.004226666844186674</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -7503,12 +7891,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
+          <t>2018-02-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2018-11</t>
+          <t>2018-02</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7651,25 +8039,25 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2018-12-01</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2018-12</t>
+          <t>2018-03</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.008453333688373348</v>
+        <v>0.004226666844186674</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -7769,12 +8157,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7799,25 +8187,25 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2018-04-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2018-04</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>167</v>
+        <v>2</v>
       </c>
       <c r="O47" t="n">
-        <v>167</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>0.08049920710811663</v>
+        <v>0.008453333688373348</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -7850,42 +8238,42 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7917,12 +8305,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7947,104 +8335,93 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2018-05-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2018-05</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O48" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>0.008453333688373348</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8071,17 +8448,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -8106,179 +8483,93 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2018-06</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>Toxóplasmasýking</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG49" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN49" t="b">
         <v>1</v>
       </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.004226666844186674</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8310,12 +8601,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -8340,25 +8631,25 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2018-07</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>190</v>
+        <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>190</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>0.09158592425474346</v>
+        <v>0.004226666844186674</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -8391,42 +8682,42 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8488,25 +8779,25 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2018-08</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.004224018720850971</v>
+        <v>0.008453333688373348</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -8606,12 +8897,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8636,25 +8927,25 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2019-03</t>
+          <t>2018-09</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>219</v>
+        <v>2</v>
       </c>
       <c r="O52" t="n">
-        <v>219</v>
+        <v>2</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.105564828483099</v>
+        <v>0.008453333688373348</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -8687,42 +8978,42 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8784,25 +9075,25 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2018-11-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2019-03</t>
+          <t>2018-11</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>0.01267205616255291</v>
+        <v>0.008453333688373348</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8902,12 +9193,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8932,25 +9223,25 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2018-12-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2018-12</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>206</v>
+        <v>2</v>
       </c>
       <c r="O54" t="n">
-        <v>206</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0.09929842313935344</v>
+        <v>0.008453333688373348</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -8983,42 +9274,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9080,25 +9371,25 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2019-05</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="O55" t="n">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.105564828483099</v>
+        <v>0.08049920710811663</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -9198,12 +9489,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -9228,93 +9519,104 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2019-05</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N56" t="n">
+        <v>134</v>
+      </c>
+      <c r="O56" t="n">
+        <v>134</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.2038659712686818</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT56" t="n">
         <v>1</v>
       </c>
-      <c r="O56" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0.004224018720850971</v>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP56" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
-      <c r="AT56" t="n">
-        <v>0</v>
-      </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -9341,17 +9643,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -9376,93 +9678,179 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2019-06</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>214</v>
+        <v>134</v>
       </c>
       <c r="O57" t="n">
-        <v>214</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0.1031546725816584</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>134</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN57" t="b">
+        <v>1</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9882,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9524,93 +9912,104 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2019-06</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.004224018720850971</v>
+        <v>0</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -9637,17 +10036,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9672,93 +10071,179 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2019-07</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>245</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0.1180976391705902</v>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Toxóplasmasýking</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN59" t="b">
+        <v>1</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -9790,12 +10275,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9820,25 +10305,25 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2019-07</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2</v>
+        <v>190</v>
       </c>
       <c r="O60" t="n">
-        <v>2</v>
+        <v>190</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0.008448037441701943</v>
+        <v>0.09158592425474346</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -9871,42 +10356,42 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -9938,12 +10423,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9968,25 +10453,25 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2019-08</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>329</v>
+        <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>329</v>
+        <v>1</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0.1585882583147926</v>
+        <v>0.004224018720850971</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -10019,42 +10504,42 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10086,12 +10571,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -10116,25 +10601,25 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2019-08</t>
+          <t>2019-03</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>219</v>
       </c>
       <c r="O62" t="n">
-        <v>2</v>
+        <v>219</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0.008448037441701943</v>
+        <v>0.105564828483099</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -10167,42 +10652,42 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -10234,12 +10719,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -10264,25 +10749,25 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2019-09</t>
+          <t>2019-03</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>281</v>
+        <v>3</v>
       </c>
       <c r="O63" t="n">
-        <v>281</v>
+        <v>3</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>0.1354507616609627</v>
+        <v>0.01267205616255291</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -10315,42 +10800,42 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10382,12 +10867,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -10412,25 +10897,25 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2019-09</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>206</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>206</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.004224018720850971</v>
+        <v>0.09929842313935344</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -10463,42 +10948,42 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -10560,25 +11045,25 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2019-05</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>284</v>
+        <v>219</v>
       </c>
       <c r="O65" t="n">
-        <v>284</v>
+        <v>219</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>0.1368968552018271</v>
+        <v>0.105564828483099</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -10708,25 +11193,25 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2019-05</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0.008448037441701943</v>
+        <v>0.004224018720850971</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -10856,25 +11341,25 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2019-11</t>
+          <t>2019-06</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="O67" t="n">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>0.1253281068749121</v>
+        <v>0.1031546725816584</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -11004,25 +11489,25 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2019-11</t>
+          <t>2019-06</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>0.008448037441701943</v>
+        <v>0.004224018720850971</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -11152,25 +11637,25 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2019-12</t>
+          <t>2019-07</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O69" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>0.1176156079903021</v>
+        <v>0.1180976391705902</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -11300,25 +11785,25 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2019-12</t>
+          <t>2019-07</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>0.004224018720850971</v>
+        <v>0.008448037441701943</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -11385,6 +11870,1486 @@
         </is>
       </c>
       <c r="BC70" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>329</v>
+      </c>
+      <c r="O71" t="n">
+        <v>329</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0.1585882583147926</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>2</v>
+      </c>
+      <c r="O72" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0.008448037441701943</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2019-09-01</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>281</v>
+      </c>
+      <c r="O73" t="n">
+        <v>281</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0.1354507616609627</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2019-09-01</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.004224018720850971</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2019-10-01</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>284</v>
+      </c>
+      <c r="O75" t="n">
+        <v>284</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0.1368968552018271</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2019-10-01</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>2</v>
+      </c>
+      <c r="O76" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.008448037441701943</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>260</v>
+      </c>
+      <c r="O77" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0.1253281068749121</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>2</v>
+      </c>
+      <c r="O78" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.008448037441701943</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>244</v>
+      </c>
+      <c r="O79" t="n">
+        <v>244</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0.1176156079903021</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.004224018720850971</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -11506,7 +13471,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -11516,7 +13481,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
@@ -11536,7 +13501,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -11546,7 +13511,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -11568,7 +13533,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2940</v>
+        <v>3819</v>
       </c>
     </row>
     <row r="16">
